--- a/Team-Data/2011-12/4-9-2011-12.xlsx
+++ b/Team-Data/2011-12/4-9-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -778,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
@@ -933,7 +1000,7 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -960,19 +1027,19 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
@@ -984,7 +1051,7 @@
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -993,7 +1060,7 @@
         <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1052,7 +1119,7 @@
         <v>4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N4" t="n">
         <v>0.301</v>
@@ -1064,10 +1131,10 @@
         <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S4" t="n">
         <v>28.9</v>
@@ -1076,7 +1143,7 @@
         <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V4" t="n">
         <v>14.3</v>
@@ -1085,13 +1152,13 @@
         <v>6.3</v>
       </c>
       <c r="X4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA4" t="n">
         <v>20.2</v>
@@ -1100,10 +1167,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.1</v>
+        <v>-12.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1154,7 +1221,7 @@
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
@@ -1163,13 +1230,13 @@
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1300,10 +1367,10 @@
         <v>26</v>
       </c>
       <c r="AI5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>9</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>8</v>
       </c>
       <c r="AK5" t="n">
         <v>11</v>
@@ -1321,7 +1388,7 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>-6.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
         <v>26</v>
@@ -1485,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1497,7 +1564,7 @@
         <v>14</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1512,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -1521,13 +1588,13 @@
         <v>20</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
@@ -1661,13 +1728,13 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
         <v>19</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK7" t="n">
         <v>21</v>
@@ -1682,19 +1749,19 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
         <v>14</v>
@@ -1703,7 +1770,7 @@
         <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.544</v>
+        <v>0.536</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
       </c>
       <c r="I8" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J8" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L8" t="n">
         <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.327</v>
+        <v>0.324</v>
       </c>
       <c r="O8" t="n">
         <v>20.2</v>
@@ -1792,19 +1859,19 @@
         <v>27.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="R8" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S8" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T8" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
         <v>15.6</v>
@@ -1813,43 +1880,43 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.5</v>
+        <v>103.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
         <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1870,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
         <v>27</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
         <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J9" t="n">
         <v>78.90000000000001</v>
@@ -1962,31 +2029,31 @@
         <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="N9" t="n">
         <v>0.341</v>
       </c>
       <c r="O9" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P9" t="n">
         <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="T9" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="V9" t="n">
         <v>15.9</v>
@@ -2001,19 +2068,19 @@
         <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB9" t="n">
         <v>90.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.8</v>
+        <v>-5.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2046,7 +2113,7 @@
         <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
@@ -2064,16 +2131,16 @@
         <v>27</v>
       </c>
       <c r="AU9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J10" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L10" t="n">
         <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O10" t="n">
         <v>14.9</v>
       </c>
       <c r="P10" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R10" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T10" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="U10" t="n">
         <v>22.3</v>
@@ -2177,25 +2244,25 @@
         <v>8.1</v>
       </c>
       <c r="X10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.7</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2210,13 +2277,13 @@
         <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
         <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2225,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="n">
         <v>29</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2258,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
         <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O11" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P11" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0.787</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S11" t="n">
         <v>30.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U11" t="n">
         <v>21.2</v>
@@ -2356,10 +2423,10 @@
         <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y11" t="n">
         <v>5.2</v>
@@ -2371,16 +2438,16 @@
         <v>18.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
         <v>1.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2407,10 +2474,10 @@
         <v>17</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2437,7 +2504,7 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.614</v>
+        <v>0.607</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,10 +2566,10 @@
         <v>35.3</v>
       </c>
       <c r="J12" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>5.7</v>
@@ -2511,55 +2578,55 @@
         <v>15.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O12" t="n">
         <v>20.3</v>
       </c>
       <c r="P12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
         <v>0.779</v>
       </c>
       <c r="R12" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S12" t="n">
         <v>31.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="V12" t="n">
         <v>14.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X12" t="n">
         <v>5.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA12" t="n">
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,13 +2638,13 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2601,13 +2668,13 @@
         <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>30</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -2663,43 +2730,43 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
         <v>34</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.596</v>
+        <v>0.607</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M13" t="n">
         <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
         <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q13" t="n">
         <v>0.681</v>
@@ -2708,19 +2775,19 @@
         <v>12.2</v>
       </c>
       <c r="S13" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="T13" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V13" t="n">
         <v>13.4</v>
       </c>
       <c r="W13" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X13" t="n">
         <v>4.7</v>
@@ -2735,22 +2802,22 @@
         <v>21.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.2</v>
+        <v>97.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH13" t="n">
         <v>7</v>
@@ -2771,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
         <v>19</v>
@@ -2783,10 +2850,10 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="n">
         <v>18</v>
@@ -2798,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>22</v>
@@ -2810,13 +2877,13 @@
         <v>24</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.621</v>
+        <v>0.614</v>
       </c>
       <c r="H14" t="n">
         <v>48.5</v>
       </c>
       <c r="I14" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J14" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.457</v>
@@ -2872,10 +2939,10 @@
         <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.318</v>
+        <v>0.316</v>
       </c>
       <c r="O14" t="n">
         <v>18.3</v>
@@ -2884,7 +2951,7 @@
         <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R14" t="n">
         <v>11.9</v>
@@ -2899,7 +2966,7 @@
         <v>22</v>
       </c>
       <c r="V14" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W14" t="n">
         <v>5.8</v>
@@ -2911,7 +2978,7 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="AA14" t="n">
         <v>20.3</v>
@@ -2923,7 +2990,7 @@
         <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2962,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>12</v>
@@ -2989,13 +3056,13 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA14" t="n">
         <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
         <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.589</v>
+        <v>0.582</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3045,10 +3112,10 @@
         <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L15" t="n">
         <v>4.1</v>
@@ -3075,16 +3142,16 @@
         <v>29.8</v>
       </c>
       <c r="T15" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U15" t="n">
         <v>19.7</v>
       </c>
       <c r="V15" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X15" t="n">
         <v>5.2</v>
@@ -3102,16 +3169,16 @@
         <v>95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>10</v>
       </c>
       <c r="AF15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG15" t="n">
         <v>10</v>
@@ -3123,10 +3190,10 @@
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3147,16 +3214,16 @@
         <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
@@ -3168,7 +3235,7 @@
         <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ15" t="n">
         <v>18</v>
@@ -3180,7 +3247,7 @@
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -3287,22 +3354,22 @@
         <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3323,10 +3390,10 @@
         <v>5</v>
       </c>
       <c r="AP16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>8</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>26</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3347,7 +3414,7 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>0.491</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,7 +3476,7 @@
         <v>38</v>
       </c>
       <c r="J17" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K17" t="n">
         <v>0.443</v>
@@ -3421,31 +3488,31 @@
         <v>19.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O17" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T17" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W17" t="n">
         <v>8.4</v>
@@ -3463,19 +3530,19 @@
         <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>19</v>
@@ -3490,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
         <v>14</v>
@@ -3508,7 +3575,7 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR17" t="n">
         <v>5</v>
@@ -3520,22 +3587,22 @@
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW17" t="n">
         <v>5</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
         <v>19</v>
@@ -3544,7 +3611,7 @@
         <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>0.431</v>
+        <v>0.439</v>
       </c>
       <c r="H18" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J18" t="n">
         <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
@@ -3603,28 +3670,28 @@
         <v>21.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O18" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P18" t="n">
         <v>25.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T18" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="n">
         <v>15.3</v>
@@ -3633,7 +3700,7 @@
         <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
@@ -3642,16 +3709,16 @@
         <v>18.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3675,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
@@ -3690,10 +3757,10 @@
         <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>8</v>
@@ -3711,7 +3778,7 @@
         <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3918,7 @@
         <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3872,7 +3939,7 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>8</v>
@@ -3893,7 +3960,7 @@
         <v>16</v>
       </c>
       <c r="AX19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3961,22 +4028,22 @@
         <v>0.449</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M20" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.341</v>
+        <v>0.335</v>
       </c>
       <c r="O20" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P20" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R20" t="n">
         <v>11.2</v>
@@ -3985,13 +4052,13 @@
         <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U20" t="n">
         <v>20.8</v>
       </c>
       <c r="V20" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W20" t="n">
         <v>7.3</v>
@@ -4006,16 +4073,16 @@
         <v>20.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,13 +4094,13 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
@@ -4045,22 +4112,22 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS20" t="n">
         <v>19</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4069,13 +4136,13 @@
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW20" t="n">
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4084,7 +4151,7 @@
         <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4221,7 +4288,7 @@
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
@@ -4248,7 +4315,7 @@
         <v>12</v>
       </c>
       <c r="AU21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
         <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,7 +4386,7 @@
         <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.475</v>
@@ -4340,10 +4407,10 @@
         <v>26.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.801</v>
+        <v>0.798</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S22" t="n">
         <v>32.5</v>
@@ -4358,7 +4425,7 @@
         <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X22" t="n">
         <v>8</v>
@@ -4367,31 +4434,31 @@
         <v>4.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.8</v>
+        <v>102.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>10</v>
@@ -4421,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" t="n">
         <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J23" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L23" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
         <v>26.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.382</v>
+        <v>0.379</v>
       </c>
       <c r="O23" t="n">
         <v>15.5</v>
@@ -4522,7 +4589,7 @@
         <v>23.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.654</v>
+        <v>0.651</v>
       </c>
       <c r="R23" t="n">
         <v>11</v>
@@ -4534,16 +4601,16 @@
         <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W23" t="n">
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
         <v>4.1</v>
@@ -4552,28 +4619,28 @@
         <v>17.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4618,10 +4685,10 @@
         <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
         <v>15</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
@@ -4767,13 +4834,13 @@
         <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4803,10 +4870,10 @@
         <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
         <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.526</v>
+        <v>0.518</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J25" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
@@ -4883,31 +4950,31 @@
         <v>16.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R25" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U25" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V25" t="n">
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y25" t="n">
         <v>4.3</v>
@@ -4919,13 +4986,13 @@
         <v>19.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>97.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4940,13 +5007,13 @@
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4964,10 +5031,10 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
         <v>14</v>
@@ -4976,13 +5043,13 @@
         <v>19</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" t="n">
         <v>27</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.466</v>
+        <v>0.474</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.445</v>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M26" t="n">
         <v>20.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O26" t="n">
         <v>17.1</v>
       </c>
       <c r="P26" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R26" t="n">
         <v>11</v>
@@ -5080,7 +5147,7 @@
         <v>40.8</v>
       </c>
       <c r="U26" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V26" t="n">
         <v>14.1</v>
@@ -5101,13 +5168,13 @@
         <v>20</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5128,7 +5195,7 @@
         <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5143,16 +5210,16 @@
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5167,13 +5234,13 @@
         <v>12</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
@@ -5182,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-5.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5355,7 +5422,7 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>9</v>
@@ -5364,7 +5431,7 @@
         <v>9</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
         <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.727</v>
+        <v>0.741</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
@@ -5411,10 +5478,10 @@
         <v>39.1</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5423,13 +5490,13 @@
         <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.385</v>
+        <v>0.387</v>
       </c>
       <c r="O28" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0.736</v>
@@ -5438,58 +5505,58 @@
         <v>10.4</v>
       </c>
       <c r="S28" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T28" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V28" t="n">
         <v>13.4</v>
       </c>
       <c r="W28" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>102</v>
+        <v>102.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2</v>
       </c>
-      <c r="AG28" t="n">
-        <v>3</v>
-      </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5501,28 +5568,28 @@
         <v>7</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5534,10 +5601,10 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
         <v>21</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G29" t="n">
-        <v>0.345</v>
+        <v>0.351</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,19 +5660,19 @@
         <v>34.6</v>
       </c>
       <c r="J29" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="O29" t="n">
         <v>16.7</v>
@@ -5614,7 +5681,7 @@
         <v>21.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
@@ -5626,7 +5693,7 @@
         <v>41.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
         <v>15.1</v>
@@ -5644,37 +5711,37 @@
         <v>23.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
         <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5686,7 +5753,7 @@
         <v>20</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
         <v>17</v>
@@ -5710,7 +5777,7 @@
         <v>19</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX29" t="n">
         <v>17</v>
@@ -5725,7 +5792,7 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.517</v>
+        <v>0.509</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
       </c>
       <c r="I30" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="J30" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.455</v>
@@ -5787,13 +5854,13 @@
         <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="O30" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P30" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
         <v>0.75</v>
@@ -5802,40 +5869,40 @@
         <v>13.1</v>
       </c>
       <c r="S30" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T30" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
@@ -5850,7 +5917,7 @@
         <v>2</v>
       </c>
       <c r="AI30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ30" t="n">
         <v>3</v>
@@ -5871,7 +5938,7 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
         <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>0.228</v>
+        <v>0.214</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
         <v>82.8</v>
@@ -5963,46 +6030,46 @@
         <v>0.438</v>
       </c>
       <c r="L31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.326</v>
+        <v>0.323</v>
       </c>
       <c r="O31" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
         <v>21.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.728</v>
+        <v>0.726</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T31" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U31" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z31" t="n">
         <v>21.5</v>
@@ -6011,13 +6078,13 @@
         <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.4</v>
+        <v>-7</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,13 +6102,13 @@
         <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="n">
         <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM31" t="n">
         <v>21</v>
@@ -6050,10 +6117,10 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP31" t="n">
         <v>20</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>18</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6062,7 +6129,7 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
@@ -6071,7 +6138,7 @@
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6089,7 +6156,7 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2011-12</t>
+          <t>2012-04-09</t>
         </is>
       </c>
     </row>
